--- a/userdata.xlsx
+++ b/userdata.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11012"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sumanpahari/Documents/Pycharm/College/FaceDetection/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0007431D-88E4-3B43-A616-0C0B756ED2E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="740" windowWidth="20120" windowHeight="7760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="744" windowWidth="20124" windowHeight="7764"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>rahul@gmail.com</t>
   </si>
@@ -41,12 +35,15 @@
   <si>
     <t>UserId</t>
   </si>
+  <si>
+    <t>rahul pal</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,7 +145,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -180,27 +177,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -232,24 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -425,15 +386,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -444,7 +405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -455,7 +416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -475,31 +436,42 @@
       </c>
       <c r="C4">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>524</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/userdata.xlsx
+++ b/userdata.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sumanpahari/Documents/Pycharm/College/FaceDetection/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC383380-C667-8042-95C8-210D816D20E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="744" windowWidth="20124" windowHeight="7764"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,14 +42,14 @@
     <t>UserId</t>
   </si>
   <si>
-    <t>rahul pal</t>
+    <t>rahul1@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,7 +151,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -177,9 +183,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -211,6 +235,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -386,15 +428,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -405,7 +447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -416,9 +458,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>123</v>
@@ -427,7 +469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -438,40 +480,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>524</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A3" r:id="rId2"/>
-    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{BCC35B0A-DECF-BC47-826F-0511C063D35E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
